--- a/dataset/02_uc_from_excel/generators_template.xlsx
+++ b/dataset/02_uc_from_excel/generators_template.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="F2" t="n">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
         <v>4500</v>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
@@ -620,40 +620,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>石川火力発電所</t>
+          <t>石垣市発電所</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E4" t="n">
-        <v>300</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -667,40 +667,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gushikawa Power Plant</t>
+          <t>三原名護市発電所</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>600</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -714,25 +714,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>吉の浦火力発電所</t>
+          <t>石川火力発電所</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lng</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>105.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H6" t="n">
         <v>5000</v>
@@ -761,25 +761,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>牧港火力発電所</t>
+          <t>Gushikawa Power Plant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="F7" t="n">
-        <v>90</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="H7" t="n">
         <v>5000</v>
@@ -808,7 +808,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>本部町発電所</t>
+          <t>与那城平宮うるま市発電所</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -855,40 +855,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>本部町発電所</t>
+          <t>吉の浦火力発電所</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>lng</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>502</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>150.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -902,40 +902,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>本部町発電所</t>
+          <t>牧港火力発電所</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>oil</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>備瀬本部町発電所</t>
+          <t>本部町発電所</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -996,40 +996,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ishikawa J-Power Coal Power Plant</t>
+          <t>本部町発電所</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>coal</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
-        <v>600</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>つきしろ南城市発電所</t>
+          <t>本部町発電所</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>山川本部町発電所</t>
+          <t>本部町発電所</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>山川本部町発電所</t>
+          <t>備瀬本部町発電所</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1184,40 +1184,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>山川本部町発電所</t>
+          <t>Ishikawa J-Power Coal Power Plant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>coal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>312</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>二見名護市発電所</t>
+          <t>つきしろ南城市発電所</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>添石中城村発電所</t>
+          <t>山川本部町発電所</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>北浜中城村発電所</t>
+          <t>山川本部町発電所</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>糸満市風力発電所</t>
+          <t>山川本部町発電所</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>糸満市風力発電所</t>
+          <t>二見名護市発電所</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>本部町発電所</t>
+          <t>添石中城村発電所</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1513,42 +1513,324 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>北浜中城村発電所</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>67</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>okinawa_g023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>上地読谷村発電所</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>okinawa_g024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>糸満市風力発電所</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>okinawa_g025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>糸満市風力発電所</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>okinawa_g026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>本部町発電所</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>71</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>okinawa_g027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>松本五丁目沖縄市発電所</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>solar</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>56</v>
-      </c>
-      <c r="E23" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="D28" t="n">
+        <v>59</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>okinawa_g028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>石垣市発電所</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>91</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
